--- a/pisameet/config/pm2018_sample.xlsx
+++ b/pisameet/config/pm2018_sample.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" state="visible" r:id="rId2"/>
@@ -580,7 +580,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="51.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="15.46"/>
@@ -687,7 +687,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.91"/>
@@ -784,7 +784,7 @@
         <v>366</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>40</v>
@@ -844,7 +844,7 @@
         <v>348</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>52</v>
